--- a/backend/data/donglin/input/input_aux.xlsx
+++ b/backend/data/donglin/input/input_aux.xlsx
@@ -459,7 +459,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>江苏大王通风机械有限公司 - 辅助核算余额</t>
+          <t>甲公司（通风机械） - 辅助核算余额</t>
         </is>
       </c>
     </row>
@@ -470,6 +470,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
